--- a/.cursor/scratch/tax_turbo_parts/SF_SPLIT.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/SF_SPLIT.xlsx
@@ -39,7 +39,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -74,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -90,6 +95,8 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bundled car + home at State Farm. Previously home=Travelers, car=Geico. Feb 11 Prime charged two unbundled policies: $157.53 (HOME — replaces Travelers) and $145.25 (AUTO — leftover Prime SF in 2026 after 524 sold is ~$147). Mar–Jul combined $302.75; Aug $308.26. Home = round(bill × 157.53/302.78); auto = remainder. Only HOME → 524 INSURANCE 50/50 U1/U2 (yellow). Geico *AUTO credit $540.89 (2025-02-11) is unused auto premium — personal, not 524. No 2025 Travelers on Prime/Sapphire/BoA/Monarch. No Sep–Dec SF on Prime.</t>
+          <t>LOCKED 2026-09-20: Travelers was home insurance before for Ferdinand; Geico was for the cars. 2025 State Farm is bundled car + home. Feb 11 Prime charged two unbundled policies: $157.53 (HOME — replaces Travelers) and $145.25 (AUTO — leftover Prime SF in 2026 after 524 sold is ~$147). Mar–Jul combined $302.75; Aug $308.26. Home = round(bill × 157.53/302.78); auto = remainder. Only HOME → 524 INSURANCE 50/50 U1/U2 (yellow; do not invent a new split). Travelers leftover 2025 (Jan leftover previously noted) is 524 home, not auto — $0 on Prime/Sapphire/BoA/Monarch. Geico *AUTO credit $540.89 (2025-02-11) is unused auto premium — personal, not 524, not EPGC. No Sep–Dec SF on Prime.</t>
         </is>
       </c>
     </row>
@@ -788,11 +795,30 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Unused Geico auto premium when switching to State Farm auto. Not 524 income.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>LOCKED 2026-09-20: Geico = cars. Unused auto premium when switching to State Farm auto. Not 524. Not EPGC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Travelers leftover Jan 2025 (prior 524 home)</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>LOCKED 524 home</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>User: Travelers was home for Ferdinand. Leftover 2025 is 524 INSURANCE, not auto. $0 on cards/Monarch.</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
